--- a/docs/Dev-Files/LoRa_Modules.xlsx
+++ b/docs/Dev-Files/LoRa_Modules.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d30df2674c95b49/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView windowWidth="14400" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -79,13 +74,13 @@
     <t>Controller</t>
   </si>
   <si>
-    <t>STM32L010K4T6</t>
+    <t>STM32L072RBT6</t>
   </si>
   <si>
     <t>STMicroelectronics</t>
   </si>
   <si>
-    <t>Selected because of low power and capable of 26 GPIOs</t>
+    <t>Selected because of low power and USB capable</t>
   </si>
   <si>
     <t>LoRa and MCU Integrated</t>
@@ -130,21 +125,24 @@
     <t>ATSAMR34J18BT-I/7JX</t>
   </si>
   <si>
+    <t>Microchip</t>
+  </si>
+  <si>
     <t>Suggestion: Preferred solution is to select Single IC LoRa module SX1276S9S+T-X1 and add a low power STM32L010K4T6 MCU for communication through SPI.</t>
-  </si>
-  <si>
-    <t>Microchip</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,14 +175,151 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,12 +328,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79995117038483843"/>
+        <fgColor theme="3" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -328,6 +649,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -355,19 +689,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -383,14 +704,259 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,52 +967,55 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -458,32 +1027,62 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -741,237 +1340,237 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="29.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="24.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="6" max="6" width="50.28515625" customWidth="1"/>
-    <col min="7" max="7" width="42.28515625" customWidth="1"/>
+    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
+    <col min="7" max="7" width="42.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+    <row r="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="10">
         <v>5.21</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="26"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="10">
         <v>19.95</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="11"/>
     </row>
-    <row r="6" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
+    <row r="6" ht="25.5" customHeight="1" spans="1:6">
+      <c r="A6" s="12"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
     </row>
-    <row r="7" spans="1:6" ht="38.25" customHeight="1">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="38.25" customHeight="1" spans="1:6">
+      <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="10">
+        <v>2.2</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="32.25" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
+    <row r="8" ht="32.25" customHeight="1" spans="1:6">
+      <c r="A8" s="7"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
     </row>
-    <row r="9" spans="1:6" ht="33" customHeight="1">
-      <c r="A9" s="26" t="s">
+    <row r="9" ht="33" customHeight="1" spans="1:6">
+      <c r="A9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="7">
-        <v>34.950000000000003</v>
-      </c>
-      <c r="F9" s="8"/>
+      <c r="E9" s="10">
+        <v>34.95</v>
+      </c>
+      <c r="F9" s="11"/>
     </row>
-    <row r="10" spans="1:6" ht="21" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="11" t="s">
+    <row r="10" ht="21" customHeight="1" spans="1:6">
+      <c r="A10" s="7"/>
+      <c r="B10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="10">
         <v>15</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="17"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
     </row>
-    <row r="13" spans="1:6" ht="33" customHeight="1">
-      <c r="A13" s="26" t="s">
+    <row r="13" ht="33" customHeight="1" spans="1:6">
+      <c r="A13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="10">
         <v>17.54</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="33" customHeight="1" thickBot="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="13" t="s">
+    <row r="14" ht="33" customHeight="1" spans="1:6">
+      <c r="A14" s="21"/>
+      <c r="B14" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="19" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="25">
+        <v>8.72</v>
+      </c>
+      <c r="F14" s="26"/>
+    </row>
+    <row r="16" ht="15.75"/>
+    <row r="17" ht="44.25" customHeight="1" spans="1:6">
+      <c r="A17" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="15">
-        <v>8.7200000000000006</v>
-      </c>
-      <c r="F14" s="29"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="29"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="17" spans="1:6" ht="44.25" customHeight="1" thickBot="1">
-      <c r="A17" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
-    </row>
-    <row r="23" spans="1:6" ht="57" customHeight="1"/>
+    <row r="23" ht="57" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
@@ -982,17 +1581,18 @@
     <mergeCell ref="F13:F14"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B9" r:id="rId3"/>
-    <hyperlink ref="B10" r:id="rId4"/>
-    <hyperlink ref="B7" r:id="rId5"/>
-    <hyperlink ref="B13" r:id="rId6"/>
-    <hyperlink ref="B14" r:id="rId7"/>
-    <hyperlink ref="B5" r:id="rId8"/>
-    <hyperlink ref="B4" r:id="rId9"/>
+    <hyperlink ref="B11" r:id="rId1" display="EMB-LR1276S"/>
+    <hyperlink ref="B3" r:id="rId2" display="SX1276S9S+T-X1"/>
+    <hyperlink ref="B9" r:id="rId3" display="Adafruit Feather 32u4"/>
+    <hyperlink ref="B10" r:id="rId4" display="RAK4200"/>
+    <hyperlink ref="B13" r:id="rId5" display="STM32WL5MOCH6TR"/>
+    <hyperlink ref="B14" r:id="rId6" display="ATSAMR34J18BT-I/7JX"/>
+    <hyperlink ref="B5" r:id="rId7" display="Adafruit RFM95W"/>
+    <hyperlink ref="B4" r:id="rId8" display="RFM95W-915S2"/>
+    <hyperlink ref="B7" r:id="rId9" display="STM32L072RBT6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>